--- a/docs/SECS/SECS_GEM功能_Handler_20260729.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260729.xlsx
@@ -872,7 +872,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -2064,7 +2063,7 @@
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>[20260729] RCMD `START`。走與操作員 Start 相同的 MachineStart() 閘(Lot/2D 資料齊備才受理)。</t>
+          <t>[20260729] RCMD START。走與操作員 Start 相同的 MachineStart() 閘(Lot/2D 資料齊備才受理)。</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2088,7 @@
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>[20260729] RCMD `PAUSE`(減速暫停)。另有 `STOP`(硬停，立即停馬達)與 `HALT`(2026-07-29 新增，對齊 HT9045 的軟停，與 PAUSE 同一路徑)。</t>
+          <t>[20260729] RCMD PAUSE(減速暫停)。另有 STOP(硬停，立即停馬達)與 HALT(2026-07-29 新增，對齊 HT9045 的軟停，與 PAUSE 同一路徑)。</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2113,7 @@
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>[20260729] RCMD `ONE_CYCLE`。完成時送 CEID 41 One Cycle Finish。HCACK 據實回報：0=已啟動 / 2=機台未運轉或資料不符 / 4=已在 OneCycle 中(與 HT9045 一律回 0 不同，見規格書 §3.4)。</t>
+          <t>[20260729] RCMD ONE_CYCLE。完成時送 CEID 41 One Cycle Finish。HCACK 據實回報：0=已啟動 / 2=機台未運轉或資料不符 / 4=已在 OneCycle 中(與 HT9045 一律回 0 不同，見規格書 §3.4)。</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2138,7 @@
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>[20260729] RCMD `CLEAN_OUT`(2026-07-29 新增，對齊 HT9045)。僅能自 Normal 運轉模式進入，非 Normal 回 HCACK=2；排空後送 CEID 42 Clean Out Finish 再自動 Lot End。</t>
+          <t>[20260729] RCMD CLEAN_OUT(2026-07-29 新增，對齊 HT9045)。僅能自 Normal 運轉模式進入，非 Normal 回 HCACK=2；排空後送 CEID 42 Clean Out Finish 再自動 Lot End。</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2163,7 @@
       </c>
       <c r="E38" s="35" t="inlineStr">
         <is>
-          <t>[20260729] 測試機專屬(清針/socket 清潔)，HT-160S 無此機構。本機認得 `AUTO_CLEAN` 但回 HCACK=2「認得命令、本機不執行」，不回 1、不回 4。</t>
+          <t>[20260729] 測試機專屬(清針/socket 清潔)，HT-160S 無此機構。本機認得 AUTO_CLEAN 但回 HCACK=2「認得命令、本機不執行」，不回 1、不回 4。</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2213,7 @@
       </c>
       <c r="E40" s="35" t="inlineStr">
         <is>
-          <t>[20260729] RCMD `PP_MUSIC`。單一 pair、CP 名稱可為空字串，值 1..4 對應音效類別；空 list = 解除。為閂鎖式覆寫，可由面板 ALARM RESET / OFF BUZZER / 維修畫面按鈕解除，斷線亦自動解除。</t>
+          <t>[20260729] RCMD PP_MUSIC。單一 pair、CP 名稱可為空字串，值 1..4 對應音效類別；空 list = 解除。為閂鎖式覆寫，可由面板 ALARM RESET / OFF BUZZER / 維修畫面按鈕解除，斷線亦自動解除。</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2238,7 @@
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>[20260729] RCMD `PP_SIGNALTOWER`。RED/GREEN/YELLOW = 0關/1亮/2閃；空 list = 解除。請每次同時指定三色。註：值 2(閃)本機依既有慣例呈現為恆亮(HT-160S 塔燈全機不閃)。警報/訊息顯示中或機台自身安全異常時暫停覆寫，避免遮蔽機台紅燈。</t>
+          <t>[20260729] RCMD PP_SIGNALTOWER。RED/GREEN/YELLOW = 0關/1亮/2閃；空 list = 解除。請每次同時指定三色。註：值 2(閃)本機依既有慣例呈現為恆亮(HT-160S 塔燈全機不閃)。警報/訊息顯示中或機台自身安全異常時暫停覆寫，避免遮蔽機台紅燈。</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2309,7 @@
       </c>
       <c r="E44" s="35" t="inlineStr">
         <is>
-          <t>[20260729] 未實作。HT9045 的 `AUTHORITY_CHECK` 尚未移植。本機權限為本地管理(system\login.txt，ID/密碼/層級)，切換時送 CEID 16 Switch UserLevel。</t>
+          <t>[20260729] 未實作。HT9045 的 AUTHORITY_CHECK 尚未移植。本機權限為本地管理(system\login.txt，ID/密碼/層級)，切換時送 CEID 16 Switch UserLevel。</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>[20260729] 未實作。HT9045 的 `PP_PASSWORD` 尚未移植。本機密碼於維修畫面本地變更。</t>
+          <t>[20260729] 未實作。HT9045 的 PP_PASSWORD 尚未移植。本機密碼於維修畫面本地變更。</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4713,7 @@
       <c r="D75" s="44" t="inlineStr"/>
       <c r="E75" s="44" t="inlineStr">
         <is>
-          <t>HT9045 字典本身即無別名</t>
+          <t>HT9045 對此號的 EventDescription 只指派了號碼本身("74")，無別名文字，識別字為 RemoteProgramClose。本機逐字照抄。無發射點。</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4734,7 @@
       <c r="D76" s="42" t="inlineStr"/>
       <c r="E76" s="42" t="inlineStr">
         <is>
-          <t>HT9045 字典本身即無別名</t>
+          <t>HT9045 對此號的 EventDescription 只指派了號碼本身("75")，無別名文字，識別字為 ChangeTesterPrgToEQC。本機逐字照抄。無發射點。</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4822,7 @@
       <c r="D80" s="42" t="inlineStr"/>
       <c r="E80" s="42" t="inlineStr">
         <is>
-          <t>HT9045 字典本身即無別名</t>
+          <t>HT9045 對此號的 EventDescription 只指派了號碼本身("79 ")，無別名文字，識別字為 REVERSED79(保留位)。本機逐字照抄，故上線時 alias 亦為 "79 "。無發射點。</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6165,7 @@
       <c r="D143" s="44" t="inlineStr"/>
       <c r="E143" s="44" t="inlineStr">
         <is>
-          <t>HT9045 字典本身即無別名</t>
+          <t>HT9045 完全未指派 EventDescription(空字串)，識別字為 PickerCountWasCleared。本機逐字照抄，故 alias 為空。無發射點。</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6186,7 @@
       <c r="D144" s="42" t="inlineStr"/>
       <c r="E144" s="42" t="inlineStr">
         <is>
-          <t>HT9045 字典本身即無別名</t>
+          <t>HT9045 完全未指派 EventDescription(空字串)，識別字為 UploadPickerCount。本機逐字照抄，故 alias 為空。無發射點。</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6207,7 @@
       <c r="D145" s="44" t="inlineStr"/>
       <c r="E145" s="44" t="inlineStr">
         <is>
-          <t>HT9045 字典本身即無別名</t>
+          <t>HT9045 完全未指派 EventDescription(空字串)，識別字為 RequestPickerCount。本機逐字照抄，故 alias 為空。無發射點。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260729.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260729.xlsx
@@ -276,7 +276,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -401,6 +401,16 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -858,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="26" min="1" max="1"/>
@@ -878,9 +888,9 @@
           <t>修訂日期 Revision date</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
+      <c r="B3" s="45" t="inlineStr">
+        <is>
+          <t>2026-07-29 (第 1 版) / 2026-07-30 (第 2 版，本次)</t>
         </is>
       </c>
     </row>
@@ -1169,6 +1179,106 @@
       <c r="B31" s="29" t="inlineStr">
         <is>
           <t>CEID 表中本機真的會發射的號碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="46" t="inlineStr">
+        <is>
+          <t>2026-07-30 第 2 版修訂 Revision 2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (commit 0ea94b7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
+          <t>1. S1F23 / S1F24 Collection Event Namelist</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>由「未實作」改為「已實作」。回 L,n{L,3{CEID, CENAME, L,m{VID}}}；&lt;L[0]&gt; 全查回全部 275 個 CEID(與 HT9045 字典一致)，未註冊的 CEID 回 {CEID, '', L,0}。此訊息為字典查詢，不影響訂閱 — 事件訂閱仍由 S2F33 / S2F35 / S2F37 決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="46" t="inlineStr">
+        <is>
+          <t>2. S2F29 / S2F30 Equipment Constant Namelist</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
+        <is>
+          <t>由「未實作」改為「已實作」。回 L,n{L,6{ECID, ECNAME, ECMIN, ECMAX, ECDEF, ECUNITS}}；全查回 7 個 EC。三個界限以該 EC 自身型別編碼，未宣告者回該型別的零長度項目。EC 寫入仍走 S2F15，可寫範圍未放寬。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="46" t="inlineStr">
+        <is>
+          <t>3. 貨批起測時間</t>
+        </is>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>由「△ 無專屬 SVID」改為「O」。新增 SVID 66033 Lot Start Time (yyyy/mm/dd hh:nn:ss)，Lot Start 閂鎖、Lot End 清空，面板按鈕與 SECS LOTSTART 兩條路徑皆寫入。未加入預設 Report 1(不變動既有事件酬載)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="inlineStr">
+        <is>
+          <t>4. SVID 表</t>
+        </is>
+      </c>
+      <c r="B38" s="46" t="inlineStr">
+        <is>
+          <t>新增 66033 Lot Start Time。本機共註冊 52 個 SVID。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="46" t="inlineStr">
+        <is>
+          <t>本次未變動 Unchanged</t>
+        </is>
+      </c>
+      <c r="B40" s="46" t="inlineStr">
+        <is>
+          <t>CEID 表(1-275 與 52 個本機發射點皆不變)、其餘功能列狀態、預設 Report 1 的 13 個 SV 內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="46" t="inlineStr">
+        <is>
+          <t>驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>模擬版與真機版(關閉 SOFT_SIMULATE)建置皆 exit 0；並以 headless SECS host 對實際韌體做完整 HSMS round-trip 驗證：S1F24 全查回 L,275(30189 bytes)、CEID 6 回 13 個 VID、CEID 272 回 19 個 VID、未知 CEID 回空；S2F30 全查回 L,7 且 FT_8 界限型別正確、未知 ECID 回全零長度；SVID 66033 於 LOTSTART 前為空、之後為 2026/07/30 09:59:18，同時 SVID 1027 為 09:59:20，證明 66033 為閂鎖值而非跟著時鐘走。上機驗證待執行。</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1516,16 @@
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>[20260729] 未實作。S1 的 dispatch 無 F23 分支，會落到未識別訊息(僅記本機 log)。</t>
+          <t>S1F23:'S1F23' W
+  &lt;L [0] 
+  &gt;
+.
+[20260730] 已實作(2026-07-30 新增)。S1F23 -&gt; S1F24 回 L,n{L,3{U4 CEID, A CENAME, L,m{U4 VID}}}。&lt;L[0]&gt; 全查回全部 275 個 CEID(與 HT9045 字典逐字相同，含本機已註冊但不發射的 223 個)；指定 CEID 只回該幾筆；未註冊的 CEID 回 {CEID, '', L,0}(與 HT9045 同)。VID 清單由該 CEID 所連結的報表依序展開，順序與該事件 S6F11 內的排列一致，重複的 VID 不去除(一個 CEID 連兩張含相同 SVID 的報表時，S6F11 本來就會送兩次)。註：本訊息只是字典查詢，不等於訂閱 — 實際要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定。</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1604,18 @@
           <t>Equipment Constant Namelist Request</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="inlineStr">
         <is>
           <t>S2F29:'S2F29' W
   &lt;L [0] 
   &gt;
-.</t>
+.
+[20260730] 已實作(2026-07-30 新增)。S2F29 -&gt; S2F30 回 L,n{L,6{U4 ECID, A ECNAME, ECMIN, ECMAX, ECDEF, A ECUNITS}}。&lt;L[0]&gt; 全查回全部 7 個 EC：1501 Recipe Name、2758/2759 Tray Pitch X/Y、2760/2761 Tray Start X/Y、2762/2763 Tray Division X/Y。ECMIN / ECMAX / ECDEF 以該 EC 自身宣告的型別編碼(例如 FT_8 的 Tray X Start 回 FT_8，不是 ASCII)；未宣告上下限者回該型別的零長度項目(E5「未宣告」的表示法，與 HT9045 相同)。未註冊的 ECID 回 L,6 內名稱 / 三個界限 / 單位皆為零長度。註：本訊息為唯讀查詢；EC 寫入仍走 S2F15，維持「機台閒置才受理」與「只開放 tray 幾何」兩道限制，S2F30 不會放寬可寫範圍。</t>
         </is>
       </c>
     </row>
@@ -1942,12 +2057,12 @@
       <c r="C28" s="31" t="n"/>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
         <is>
-          <t>[20260729] 無專屬 SVID。Lot 開始以 CEID 6 Lot Start 通知，該事件帶 Report 1(含 SVID 1027 System Time)，host 可由事件時間取得起測時間；另 SVID 66031 Current Lot ID、66030 Active Lot Count 可查詢。若貴端需要獨立的「起測時間」SVID，可新增(建議置於 66000 高位段)。</t>
+          <t>[20260730] 已實作(2026-07-30 新增)。新增 SVID 66033 Lot Start Time，格式 'yyyy/mm/dd hh:nn:ss'(與 SVID 1027 System Time 同格式，可直接比對)。於 Lot Start 當下閂鎖 — 操作面板 Lot Start 按鈕與 SECS S2F41 LOTSTART 兩條路徑都會寫入 — Lot End 清空，貨批進行中可隨時以 S1F3 回查(不會隨系統時間變動)。CEID 6 Lot Start 事件照舊發送，可作為即時通知。註1：66033 未加入預設 Report 1。該報表是每個 CEID 的預設酬載，其 13 個 SV 的內容已對貴端公布，加欄位會改變線上每一筆事件的長度；若需在事件內帶出起測時間，請以 S2F33 / S2F35 將 66033 綁進貴端自訂報表即可。註2：本欄位不做斷電保存，機台中途重開後為空，直到下一次 Lot Start；持久紀錄請以 CEID 6 事件為準。</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6.5" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
@@ -2968,6 +3083,16 @@
       <c r="B52" s="37" t="inlineStr">
         <is>
           <t>Real/Dummy</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="46" t="n">
+        <v>66033</v>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>Lot Start Time</t>
         </is>
       </c>
     </row>
